--- a/users.xlsx
+++ b/users.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$C$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$C$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>序号</t>
   </si>
@@ -41,52 +41,238 @@
     <t>工号</t>
   </si>
   <si>
+    <t>蔡雷雷</t>
+  </si>
+  <si>
+    <t>01230145</t>
+  </si>
+  <si>
+    <t>宋晓迪</t>
+  </si>
+  <si>
+    <t>01230110</t>
+  </si>
+  <si>
+    <t>张小卫</t>
+  </si>
+  <si>
+    <t>01230180</t>
+  </si>
+  <si>
+    <t>陈天荣</t>
+  </si>
+  <si>
+    <t>01230044</t>
+  </si>
+  <si>
+    <t>吴婕</t>
+  </si>
+  <si>
+    <t>01220307</t>
+  </si>
+  <si>
+    <t>俞依能</t>
+  </si>
+  <si>
+    <t>01220363</t>
+  </si>
+  <si>
+    <t>陈薇</t>
+  </si>
+  <si>
+    <t>01220264</t>
+  </si>
+  <si>
+    <t>杨婕</t>
+  </si>
+  <si>
+    <t>01220280</t>
+  </si>
+  <si>
+    <t>连辉</t>
+  </si>
+  <si>
+    <t>01220281</t>
+  </si>
+  <si>
+    <t>王伟</t>
+  </si>
+  <si>
+    <t>01230189</t>
+  </si>
+  <si>
+    <t>姜宇博</t>
+  </si>
+  <si>
+    <t>01210136</t>
+  </si>
+  <si>
+    <t>马平理</t>
+  </si>
+  <si>
+    <t>01220341</t>
+  </si>
+  <si>
+    <t>吕佳辉</t>
+  </si>
+  <si>
+    <t>01230192</t>
+  </si>
+  <si>
+    <t>吴增文</t>
+  </si>
+  <si>
+    <t>01220311</t>
+  </si>
+  <si>
+    <t>肖舟旻</t>
+  </si>
+  <si>
+    <t>01220168</t>
+  </si>
+  <si>
+    <t>冯石磊</t>
+  </si>
+  <si>
+    <t>01230022</t>
+  </si>
+  <si>
+    <t>吴佳慧</t>
+  </si>
+  <si>
+    <t>01220310</t>
+  </si>
+  <si>
+    <t>贾向凯</t>
+  </si>
+  <si>
+    <t>01220335</t>
+  </si>
+  <si>
+    <t>王谦</t>
+  </si>
+  <si>
+    <t>01230063</t>
+  </si>
+  <si>
+    <t>隋杨</t>
+  </si>
+  <si>
+    <t>01220254</t>
+  </si>
+  <si>
+    <t>步泽聪</t>
+  </si>
+  <si>
+    <t>01220266</t>
+  </si>
+  <si>
+    <t>刘昌鑫</t>
+  </si>
+  <si>
+    <t>01230153</t>
+  </si>
+  <si>
+    <t>张咪</t>
+  </si>
+  <si>
+    <t>01230024</t>
+  </si>
+  <si>
+    <t>文旭鹏</t>
+  </si>
+  <si>
+    <t>01230203</t>
+  </si>
+  <si>
+    <t>李根</t>
+  </si>
+  <si>
+    <t>01220229</t>
+  </si>
+  <si>
+    <t>罗俊文</t>
+  </si>
+  <si>
+    <t>01220206</t>
+  </si>
+  <si>
+    <t>吉斌</t>
+  </si>
+  <si>
+    <t>01230097</t>
+  </si>
+  <si>
     <t>桂林</t>
   </si>
   <si>
     <t>01220244</t>
   </si>
   <si>
-    <t>陈飞03</t>
-  </si>
-  <si>
-    <t>01220180</t>
-  </si>
-  <si>
-    <t>陈天荣</t>
-  </si>
-  <si>
-    <t>01230044</t>
-  </si>
-  <si>
-    <t>隋杨</t>
-  </si>
-  <si>
-    <t>01220254</t>
-  </si>
-  <si>
-    <t>马金艳</t>
-  </si>
-  <si>
-    <t>01200043</t>
-  </si>
-  <si>
-    <t>陆扬02</t>
-  </si>
-  <si>
-    <t>01220374</t>
-  </si>
-  <si>
-    <t>宫成业</t>
-  </si>
-  <si>
-    <t>01210105</t>
-  </si>
-  <si>
-    <t>童清</t>
-  </si>
-  <si>
-    <t>01220179</t>
+    <t>查方淇</t>
+  </si>
+  <si>
+    <t>01220366</t>
+  </si>
+  <si>
+    <t>马健欣</t>
+  </si>
+  <si>
+    <t>01220238</t>
+  </si>
+  <si>
+    <t>田琪</t>
+  </si>
+  <si>
+    <t>01220181</t>
+  </si>
+  <si>
+    <t>杨林林</t>
+  </si>
+  <si>
+    <t>01220285</t>
+  </si>
+  <si>
+    <t>黄浩宁</t>
+  </si>
+  <si>
+    <t>01230094</t>
+  </si>
+  <si>
+    <t>李智超</t>
+  </si>
+  <si>
+    <t>01220343</t>
+  </si>
+  <si>
+    <t>马晓辉</t>
+  </si>
+  <si>
+    <t>01230029</t>
+  </si>
+  <si>
+    <t>朱思捷</t>
+  </si>
+  <si>
+    <t>01220301</t>
+  </si>
+  <si>
+    <t>郭振文</t>
+  </si>
+  <si>
+    <t>01230179</t>
+  </si>
+  <si>
+    <t>程文龙</t>
+  </si>
+  <si>
+    <t>01220327</t>
+  </si>
+  <si>
+    <t>徐恩惠</t>
+  </si>
+  <si>
+    <t>01220286</t>
   </si>
   <si>
     <t>刘英杰</t>
@@ -95,166 +281,70 @@
     <t>01220182</t>
   </si>
   <si>
+    <t>江连杰</t>
+  </si>
+  <si>
+    <t>01230132</t>
+  </si>
+  <si>
+    <t>徐富盛</t>
+  </si>
+  <si>
+    <t>01220221</t>
+  </si>
+  <si>
     <t>陈闯</t>
   </si>
   <si>
     <t>01230030</t>
   </si>
   <si>
-    <t>谢文雅</t>
-  </si>
-  <si>
-    <t>01220192</t>
-  </si>
-  <si>
-    <t>程文龙</t>
-  </si>
-  <si>
-    <t>01220327</t>
-  </si>
-  <si>
-    <t>陈薇02</t>
-  </si>
-  <si>
-    <t>01220264</t>
-  </si>
-  <si>
-    <t>江连杰</t>
-  </si>
-  <si>
-    <t>01230132</t>
-  </si>
-  <si>
-    <t>吴婕02</t>
-  </si>
-  <si>
-    <t>01220307</t>
-  </si>
-  <si>
-    <t>张小卫</t>
-  </si>
-  <si>
-    <t>01230180</t>
-  </si>
-  <si>
-    <t>步泽聪</t>
-  </si>
-  <si>
-    <t>01220266</t>
-  </si>
-  <si>
-    <t>刘敏02</t>
-  </si>
-  <si>
-    <t>01220329</t>
-  </si>
-  <si>
-    <t>吴佳慧02</t>
-  </si>
-  <si>
-    <t>01220310</t>
-  </si>
-  <si>
-    <t>沈贤杰</t>
-  </si>
-  <si>
-    <t>01210058</t>
-  </si>
-  <si>
-    <t>狄旻珉</t>
-  </si>
-  <si>
-    <t>01220295</t>
-  </si>
-  <si>
-    <t>徐富盛</t>
-  </si>
-  <si>
-    <t>01220221</t>
-  </si>
-  <si>
-    <t>冯石磊</t>
-  </si>
-  <si>
-    <t>01230022</t>
-  </si>
-  <si>
-    <t>贾向凯</t>
-  </si>
-  <si>
-    <t>01220335</t>
-  </si>
-  <si>
-    <t>查方淇</t>
-  </si>
-  <si>
-    <t>01220366</t>
-  </si>
-  <si>
-    <t>黄浩宁</t>
-  </si>
-  <si>
-    <t>01230094</t>
-  </si>
-  <si>
-    <t>杨婕04</t>
-  </si>
-  <si>
-    <t>01220280</t>
-  </si>
-  <si>
-    <t>杨林林</t>
-  </si>
-  <si>
-    <t>01220285</t>
-  </si>
-  <si>
-    <t>杨雨辉</t>
-  </si>
-  <si>
-    <t>01220202</t>
-  </si>
-  <si>
-    <t>口启慧</t>
-  </si>
-  <si>
-    <t>01230032</t>
-  </si>
-  <si>
-    <t>马晓辉</t>
-  </si>
-  <si>
-    <t>01230029</t>
-  </si>
-  <si>
-    <t>于鹏飞</t>
-  </si>
-  <si>
-    <t>01210131</t>
-  </si>
-  <si>
-    <t>陈市02</t>
-  </si>
-  <si>
-    <t>01230084</t>
-  </si>
-  <si>
-    <t>刘庆杰</t>
-  </si>
-  <si>
-    <t>01200044</t>
-  </si>
-  <si>
-    <t>田琪</t>
-  </si>
-  <si>
-    <t>01220181</t>
-  </si>
-  <si>
-    <t>骆积源</t>
-  </si>
-  <si>
-    <t>01220223</t>
+    <t>薛瑞</t>
+  </si>
+  <si>
+    <t>01200024</t>
+  </si>
+  <si>
+    <t>郑媛媛</t>
+  </si>
+  <si>
+    <t>01220288</t>
+  </si>
+  <si>
+    <t>马程远</t>
+  </si>
+  <si>
+    <t>01230083</t>
+  </si>
+  <si>
+    <t>徐金才</t>
+  </si>
+  <si>
+    <t>01210095</t>
+  </si>
+  <si>
+    <t>马赛民</t>
+  </si>
+  <si>
+    <t>01220265</t>
+  </si>
+  <si>
+    <t>汤佳境</t>
+  </si>
+  <si>
+    <t>01230043</t>
+  </si>
+  <si>
+    <t>方宜武</t>
+  </si>
+  <si>
+    <t>01220347</t>
+  </si>
+  <si>
+    <t>刘海波</t>
+  </si>
+  <si>
+    <t>01220381</t>
   </si>
   <si>
     <t>刘梦杰</t>
@@ -263,334 +353,16 @@
     <t>01230095</t>
   </si>
   <si>
-    <t>吴增文</t>
-  </si>
-  <si>
-    <t>01220311</t>
-  </si>
-  <si>
-    <t>徐金才</t>
-  </si>
-  <si>
-    <t>01210095</t>
-  </si>
-  <si>
-    <t>吴天皓</t>
-  </si>
-  <si>
-    <t>01210104</t>
-  </si>
-  <si>
-    <t>占启航</t>
-  </si>
-  <si>
-    <t>01220284</t>
-  </si>
-  <si>
-    <t>陆震宁</t>
-  </si>
-  <si>
-    <t>01220298</t>
-  </si>
-  <si>
-    <t>王伟09</t>
-  </si>
-  <si>
-    <t>01230189</t>
-  </si>
-  <si>
-    <t>郑媛媛</t>
-  </si>
-  <si>
-    <t>01220288</t>
-  </si>
-  <si>
-    <t>李根</t>
-  </si>
-  <si>
-    <t>01220229</t>
-  </si>
-  <si>
-    <t>郭振文</t>
-  </si>
-  <si>
-    <t>01230179</t>
-  </si>
-  <si>
-    <t>王谦03</t>
-  </si>
-  <si>
-    <t>01230063</t>
-  </si>
-  <si>
-    <t>张丹02</t>
-  </si>
-  <si>
-    <t>01210149</t>
-  </si>
-  <si>
-    <t>马健欣</t>
-  </si>
-  <si>
-    <t>01220238</t>
+    <t>罗欣</t>
+  </si>
+  <si>
+    <t>01230107</t>
   </si>
   <si>
     <t>袁维维</t>
   </si>
   <si>
     <t>01220387</t>
-  </si>
-  <si>
-    <t>徐鹏02</t>
-  </si>
-  <si>
-    <t>01220198</t>
-  </si>
-  <si>
-    <t>方宜武</t>
-  </si>
-  <si>
-    <t>01220347</t>
-  </si>
-  <si>
-    <t>韩海洋</t>
-  </si>
-  <si>
-    <t>01230028</t>
-  </si>
-  <si>
-    <t>肖舟旻</t>
-  </si>
-  <si>
-    <t>01220168</t>
-  </si>
-  <si>
-    <t>李智超</t>
-  </si>
-  <si>
-    <t>01220343</t>
-  </si>
-  <si>
-    <t>罗俊文</t>
-  </si>
-  <si>
-    <t>01220206</t>
-  </si>
-  <si>
-    <t>周德友</t>
-  </si>
-  <si>
-    <t>01230025</t>
-  </si>
-  <si>
-    <t>文旭鹏</t>
-  </si>
-  <si>
-    <t>01230203</t>
-  </si>
-  <si>
-    <t>杨念顺</t>
-  </si>
-  <si>
-    <t>01220282</t>
-  </si>
-  <si>
-    <t>罗欣</t>
-  </si>
-  <si>
-    <t>01230107</t>
-  </si>
-  <si>
-    <t>俞依能</t>
-  </si>
-  <si>
-    <t>01220363</t>
-  </si>
-  <si>
-    <t>刘昌鑫</t>
-  </si>
-  <si>
-    <t>01230153</t>
-  </si>
-  <si>
-    <t>蒋斌斌</t>
-  </si>
-  <si>
-    <t>01220269</t>
-  </si>
-  <si>
-    <t>宋晓迪</t>
-  </si>
-  <si>
-    <t>01230110</t>
-  </si>
-  <si>
-    <t>徐恩惠</t>
-  </si>
-  <si>
-    <t>01220286</t>
-  </si>
-  <si>
-    <t>荆福琪</t>
-  </si>
-  <si>
-    <t>01220313</t>
-  </si>
-  <si>
-    <t>汪桉旭</t>
-  </si>
-  <si>
-    <t>01220205</t>
-  </si>
-  <si>
-    <t>马程远</t>
-  </si>
-  <si>
-    <t>01230083</t>
-  </si>
-  <si>
-    <t>姜宇博</t>
-  </si>
-  <si>
-    <t>01210136</t>
-  </si>
-  <si>
-    <t>吕佳辉</t>
-  </si>
-  <si>
-    <t>01230192</t>
-  </si>
-  <si>
-    <t>李博</t>
-  </si>
-  <si>
-    <t>01220267</t>
-  </si>
-  <si>
-    <t>刘海波02</t>
-  </si>
-  <si>
-    <t>01220381</t>
-  </si>
-  <si>
-    <t>沈宇03</t>
-  </si>
-  <si>
-    <t>01220346</t>
-  </si>
-  <si>
-    <t>朱思捷</t>
-  </si>
-  <si>
-    <t>01220301</t>
-  </si>
-  <si>
-    <t>豆扬名</t>
-  </si>
-  <si>
-    <t>01220163</t>
-  </si>
-  <si>
-    <t>汤佳境</t>
-  </si>
-  <si>
-    <t>01230043</t>
-  </si>
-  <si>
-    <t>张咪</t>
-  </si>
-  <si>
-    <t>01230024</t>
-  </si>
-  <si>
-    <t>李世尉</t>
-  </si>
-  <si>
-    <t>01220357</t>
-  </si>
-  <si>
-    <t>马平理</t>
-  </si>
-  <si>
-    <t>01220341</t>
-  </si>
-  <si>
-    <t>吉斌</t>
-  </si>
-  <si>
-    <t>01230097</t>
-  </si>
-  <si>
-    <t>马赛民</t>
-  </si>
-  <si>
-    <t>01220265</t>
-  </si>
-  <si>
-    <t>连辉</t>
-  </si>
-  <si>
-    <t>01220281</t>
-  </si>
-  <si>
-    <t>肖志峰</t>
-  </si>
-  <si>
-    <t>01230001</t>
-  </si>
-  <si>
-    <t>王忠</t>
-  </si>
-  <si>
-    <t>01220177</t>
-  </si>
-  <si>
-    <t>周智威</t>
-  </si>
-  <si>
-    <t>01220195</t>
-  </si>
-  <si>
-    <t>蔡雷雷</t>
-  </si>
-  <si>
-    <t>01230145</t>
-  </si>
-  <si>
-    <t>毛翔</t>
-  </si>
-  <si>
-    <t>01220272</t>
-  </si>
-  <si>
-    <t>薛瑞</t>
-  </si>
-  <si>
-    <t>01200024</t>
-  </si>
-  <si>
-    <t>黄晓巍</t>
-  </si>
-  <si>
-    <t>01220270</t>
-  </si>
-  <si>
-    <t>万凯文</t>
-  </si>
-  <si>
-    <t>01220189</t>
-  </si>
-  <si>
-    <t>陈博文</t>
-  </si>
-  <si>
-    <t>01210087</t>
-  </si>
-  <si>
-    <t>徐庶</t>
-  </si>
-  <si>
-    <t>01200042</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1354,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultColWidth="21" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3">
@@ -2190,426 +1962,8 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" ht="16.5" spans="1:3">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" ht="16.5" spans="1:3">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:3">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" ht="16.5" spans="1:3">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:3">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:3">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:3">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:3">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:3">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:3">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:3">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:3">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:3">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" ht="16.5" spans="1:3">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" ht="16.5" spans="1:3">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:3">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="72" ht="16.5" spans="1:3">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="73" ht="16.5" spans="1:3">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="74" ht="16.5" spans="1:3">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:3">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" ht="16.5" spans="1:3">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" ht="16.5" spans="1:3">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="78" ht="16.5" spans="1:3">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="79" ht="16.5" spans="1:3">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="80" ht="16.5" spans="1:3">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="81" ht="16.5" spans="1:3">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="82" ht="16.5" spans="1:3">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="83" ht="16.5" spans="1:3">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="84" ht="16.5" spans="1:3">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="85" ht="16.5" spans="1:3">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="86" ht="16.5" spans="1:3">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="87" ht="16.5" spans="1:3">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="88" ht="16.5" spans="1:3">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="89" ht="16.5" spans="1:3">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="90" ht="16.5" spans="1:3">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="91" ht="16.5" spans="1:3">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="92" ht="16.5" spans="1:3">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="93" ht="16.5" spans="1:3">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:C93">
+  <autoFilter ref="B1:C55">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
